--- a/artfynd/A 32487-2021 artfynd.xlsx
+++ b/artfynd/A 32487-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130669692</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32487-2021 artfynd.xlsx
+++ b/artfynd/A 32487-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130669692</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32487-2021 artfynd.xlsx
+++ b/artfynd/A 32487-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130669692</v>
       </c>
       <c r="B2" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32487-2021 artfynd.xlsx
+++ b/artfynd/A 32487-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130669692</v>
       </c>
       <c r="B2" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32487-2021 artfynd.xlsx
+++ b/artfynd/A 32487-2021 artfynd.xlsx
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>Liam Martin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 32487-2021 artfynd.xlsx
+++ b/artfynd/A 32487-2021 artfynd.xlsx
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Martin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 32487-2021 artfynd.xlsx
+++ b/artfynd/A 32487-2021 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>131106007</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131106008</v>
+        <v>131106010</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,26 +943,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svartåsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612048</v>
+        <v>612376</v>
       </c>
       <c r="R4" t="n">
-        <v>6945825</v>
+        <v>6945396</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +980,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2025_1182</t>
+          <t>2025_1180</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -999,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131106010</v>
+        <v>131106008</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,17 +1059,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svartåsen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>612376</v>
+        <v>612048</v>
       </c>
       <c r="R5" t="n">
-        <v>6945396</v>
+        <v>6945825</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025_1180</t>
+          <t>2025_1182</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,7 +1159,7 @@
         <v>131106009</v>
       </c>
       <c r="B6" t="n">
-        <v>79864</v>
+        <v>79865</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32487-2021 artfynd.xlsx
+++ b/artfynd/A 32487-2021 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>131106007</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131106010</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>131106008</v>
       </c>
       <c r="B5" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>131106009</v>
       </c>
       <c r="B6" t="n">
-        <v>79865</v>
+        <v>79867</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32487-2021 artfynd.xlsx
+++ b/artfynd/A 32487-2021 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>131106007</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131106010</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>131106008</v>
       </c>
       <c r="B5" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>131106009</v>
       </c>
       <c r="B6" t="n">
-        <v>79867</v>
+        <v>79868</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32487-2021 artfynd.xlsx
+++ b/artfynd/A 32487-2021 artfynd.xlsx
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131106010</v>
+        <v>131106008</v>
       </c>
       <c r="B4" t="n">
         <v>79249</v>
@@ -943,17 +943,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svartåsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612376</v>
+        <v>612048</v>
       </c>
       <c r="R4" t="n">
-        <v>6945396</v>
+        <v>6945825</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +989,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2025_1180</t>
+          <t>2025_1182</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -990,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,7 +1040,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131106008</v>
+        <v>131106010</v>
       </c>
       <c r="B5" t="n">
         <v>79249</v>
@@ -1059,26 +1068,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svartåsen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>612048</v>
+        <v>612376</v>
       </c>
       <c r="R5" t="n">
-        <v>6945825</v>
+        <v>6945396</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025_1182</t>
+          <t>2025_1180</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 32487-2021 artfynd.xlsx
+++ b/artfynd/A 32487-2021 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>131106007</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131106008</v>
+        <v>131106010</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,26 +943,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svartåsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612048</v>
+        <v>612376</v>
       </c>
       <c r="R4" t="n">
-        <v>6945825</v>
+        <v>6945396</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +980,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2025_1182</t>
+          <t>2025_1180</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -999,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131106010</v>
+        <v>131106008</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,17 +1059,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svartåsen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>612376</v>
+        <v>612048</v>
       </c>
       <c r="R5" t="n">
-        <v>6945396</v>
+        <v>6945825</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025_1180</t>
+          <t>2025_1182</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,7 +1159,7 @@
         <v>131106009</v>
       </c>
       <c r="B6" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32487-2021 artfynd.xlsx
+++ b/artfynd/A 32487-2021 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>131106007</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131106010</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>131106008</v>
       </c>
       <c r="B5" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>131106009</v>
       </c>
       <c r="B6" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32487-2021 artfynd.xlsx
+++ b/artfynd/A 32487-2021 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>131106007</v>
       </c>
       <c r="B3" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131106010</v>
       </c>
       <c r="B4" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>131106008</v>
       </c>
       <c r="B5" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>131106009</v>
       </c>
       <c r="B6" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32487-2021 artfynd.xlsx
+++ b/artfynd/A 32487-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130669692</v>
+        <v>131106007</v>
       </c>
       <c r="B2" t="n">
-        <v>57881</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lidbackberget, Mpd</t>
+          <t>Svartåsen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612039</v>
+        <v>612036</v>
       </c>
       <c r="R2" t="n">
-        <v>6945492</v>
+        <v>6945843</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,17 +749,27 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>2025_1183</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,12 +784,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,14 +800,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131106007</v>
+        <v>131106008</v>
       </c>
       <c r="B3" t="n">
-        <v>79254</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -820,7 +830,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612036</v>
+        <v>612048</v>
       </c>
       <c r="R3" t="n">
-        <v>6945843</v>
+        <v>6945825</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +874,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2025_1183</t>
+          <t>2025_1182</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Jennifer Lehikoinen, Måns Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -918,11 +928,11 @@
         <v>131106010</v>
       </c>
       <c r="B4" t="n">
-        <v>79254</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1031,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131106008</v>
+        <v>131106001</v>
       </c>
       <c r="B5" t="n">
-        <v>79254</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,31 +1052,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1075,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>612048</v>
+        <v>612027</v>
       </c>
       <c r="R5" t="n">
-        <v>6945825</v>
+        <v>6945919</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1115,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025_1182</t>
+          <t>2025_1189</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1115,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1135,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,7 +1169,7 @@
         <v>131106009</v>
       </c>
       <c r="B6" t="n">
-        <v>79873</v>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,6 +1289,236 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130669692</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lidbackberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>612039</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6945492</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann, Liam Martin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130669695</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lidbackberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>611983</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6945636</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>556</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann, Liam Martin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>
